--- a/stories/arbres/ATOM-FAM.AID.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1289,6 +1305,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Damien veut ouvrir le bocal. Le couvercle est dur. Damien sent ses mains fatiguées. Il va vers eux. Papa et maman sont dans la cuisine. Damien dit le besoin : j'ai besoin d'aide. Papa tient le bocal. Plus tard, le puzzle est trop dur. Damien va vers eux. Il dit le besoin. Maman écoute. Même leçon, autre objet. Aller vers eux. Dire le besoin. Papa sourit. Maman tend une pièce.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1486,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Damien ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1655,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Damien est allé vers eux. Il a dit le besoin. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1818,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le bocal est ouvert. Damien pose une pièce du puzzle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1985,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2025,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1310,6 +1315,7 @@
           <t>narrateur|Damien veut ouvrir le bocal. Le couvercle est dur. Damien sent ses mains fatiguées. Il va vers eux. Papa et maman sont dans la cuisine. Damien dit le besoin : j'ai besoin d'aide. Papa tient le bocal. Plus tard, le puzzle est trop dur. Damien va vers eux. Il dit le besoin. Maman écoute. Même leçon, autre objet. Aller vers eux. Dire le besoin. Papa sourit. Maman tend une pièce.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1499,7 @@
           <t>narrateur|C'est trop difficile. Que fait Damien ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1660,6 +1667,7 @@
           <t>narrateur|Damien est allé vers eux. Il a dit le besoin. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1823,6 +1831,7 @@
           <t>narrateur|Le bocal est ouvert. Damien pose une pièce du puzzle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1990,6 +1999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2008,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2042,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2257,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Damien va vers papa et maman</t>
+          <t>Le bocal de miel de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut du miel. Le couvercle est dur. Il va vers papa et maman. Il dit le besoin. Plus tard, le puzzle aussi.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Damien veut ouvrir le bocal. Le couvercle est dur. Damien sent ses mains fatiguées. Il va vers eux. Papa et maman sont dans la cuisine. Damien dit le besoin : j'ai besoin d'aide. Papa tient le bocal. Plus tard, le puzzle est trop dur. Damien va vers eux. Il dit le besoin. Maman écoute. Même leçon, autre objet. Aller vers eux. Dire le besoin. Papa sourit. Maman tend une pièce.</t>
+          <t>Derrière la vitre, les toits du village sont gris-bleu. Le ciel est pâle, presque blanc. Une cheminée laisse un filet de fumée. Un chat marche sur le muret. Ses pattes ne font aucun bruit. Dans la cuisine, l'horloge fait tic-tac. Le bois de la table est lisse, un peu chaud. Papa et maman sont à table. Deux tasses fument tout doux. Ça sent le thé, Raphaël. Le pain est encore un peu chaud. La croûte craque sous le couteau. J'entends le chat ? Il est sur le muret. Il se promène, tout calme. Un bocal de miel brille près de l'assiette. Le miel est doré et épais. Je voudrais du miel. Il est dans le bocal, tout près. En ce moment, Raphaël prend le bocal. Le verre est lisse et froid. Il tourne le couvercle. Le couvercle reste collé. Ses mains sont un peu fatiguées. C'est trop difficile. Tu peux venir vers nous. Tu peux dire le besoin. Raphaël va vers eux. Il pose le bocal sur la table. J'ai besoin d'aide. Le couvercle est trop dur. Merci d'être venu le dire. On tient le bocal ensemble. Papa tient le bocal. Raphaël tourne un peu. Le couvercle fait clic. Bravo, Raphaël. Tu es allé vers nous. Tu as dit le besoin. Le miel sent bon. Une petite cuillère, tout doux. Le miel coule, lent et doré. Raphaël goûte une goutte. C'est sucré. Tu as demandé, et on a entendu. Plus tard, au salon, un puzzle attend. Les pièces sont sur le tapis. Le tapis est beige et doux. Une pièce bleue manque au ciel. Cette pièce ne rentre pas. Raphaël cherche, puis s'arrête. Il se souvient du bocal. Il va vers maman. Maman, j'ai besoin d'aide. Le puzzle est trop dur. Tu es venu vers nous. Tu as dit le besoin. C'est du bon travail. Demander, ce n'est pas être petit. C'est parler, tout simplement. Maman tend une pièce bleue. Raphaël la pose. Le ciel du puzzle devient entier. Elle rentre. Bravo. Aller vers eux, puis dire le besoin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Damien veut ouvrir le bocal. Le couvercle est dur. Damien sent ses mains fatiguées. Il va vers eux. Papa et maman sont dans la cuisine. Damien dit le besoin : j'ai besoin d'aide. Papa tient le bocal. Plus tard, le puzzle est trop dur. Damien va vers eux. Il dit le besoin. Maman écoute. Même leçon, autre objet. Aller vers eux. Dire le besoin. Papa sourit. Maman tend une pièce.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Derrière la vitre, les toits du village sont gris-bleu.
+narrateur|Le ciel est pâle, presque blanc.
+narrateur|Une cheminée laisse un filet de fumée.
+narrateur|Un chat marche sur le muret.
+narrateur|Ses pattes ne font aucun bruit.
+narrateur|Dans la cuisine, l'horloge fait tic-tac.
+narrateur|Le bois de la table est lisse, un peu chaud.
+narrateur|Papa et maman sont à table.
+narrateur|Deux tasses fument tout doux.
+papa|Ça sent le thé, Raphaël.
+maman|Le pain est encore un peu chaud.
+narrateur|La croûte craque sous le couteau.
+enfant-m|J'entends le chat ?
+papa|Il est sur le muret.
+maman|Il se promène, tout calme.
+narrateur|Un bocal de miel brille près de l'assiette.
+narrateur|Le miel est doré et épais.
+enfant-m|Je voudrais du miel.
+maman|Il est dans le bocal, tout près.
+narrateur|En ce moment, Raphaël prend le bocal.
+narrateur|Le verre est lisse et froid.
+narrateur|Il tourne le couvercle.
+narrateur|Le couvercle reste collé.
+narrateur|Ses mains sont un peu fatiguées.
+enfant-m|C'est trop difficile.
+papa|Tu peux venir vers nous.
+maman|Tu peux dire le besoin.
+narrateur|Raphaël va vers eux.
+narrateur|Il pose le bocal sur la table.
+enfant-m|J'ai besoin d'aide.
+enfant-m|Le couvercle est trop dur.
+papa|Merci d'être venu le dire.
+papa|On tient le bocal ensemble.
+narrateur|Papa tient le bocal.
+narrateur|Raphaël tourne un peu.
+narrateur|Le couvercle fait clic.
+maman|Bravo, Raphaël.
+maman|Tu es allé vers nous.
+maman|Tu as dit le besoin.
+enfant-m|Le miel sent bon.
+papa|Une petite cuillère, tout doux.
+narrateur|Le miel coule, lent et doré.
+narrateur|Raphaël goûte une goutte.
+enfant-m|C'est sucré.
+maman|Tu as demandé, et on a entendu.
+narrateur|Plus tard, au salon, un puzzle attend.
+narrateur|Les pièces sont sur le tapis.
+narrateur|Le tapis est beige et doux.
+narrateur|Une pièce bleue manque au ciel.
+enfant-m|Cette pièce ne rentre pas.
+narrateur|Raphaël cherche, puis s'arrête.
+narrateur|Il se souvient du bocal.
+narrateur|Il va vers maman.
+enfant-m|Maman, j'ai besoin d'aide.
+enfant-m|Le puzzle est trop dur.
+maman|Tu es venu vers nous.
+maman|Tu as dit le besoin.
+maman|C'est du bon travail.
+papa|Demander, ce n'est pas être petit.
+papa|C'est parler, tout simplement.
+narrateur|Maman tend une pièce bleue.
+narrateur|Raphaël la pose.
+narrateur|Le ciel du puzzle devient entier.
+enfant-m|Elle rentre.
+maman|Bravo.
+papa|Aller vers eux, puis dire le besoin.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1340,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>C'est trop difficile. Que fait Damien ?</t>
+          <t>C'est trop difficile. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1417,7 +1498,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
@@ -1496,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|C'est trop difficile. Que fait Damien ?</t>
+          <t>narrateur|C'est trop difficile.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1524,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Damien est allé vers eux. Il a dit le besoin. Papa et maman ont écouté.</t>
+          <t>Raphaël est allé vers eux. Il a dit le besoin. Tu es venu nous voir. Tu as dit : j'ai besoin d'aide. Papa a tenu le bocal. Maman a tendu la pièce. Aller vers eux. Dire le besoin. Bravo, Raphaël. Tu as fait du bon travail. Deux fois, tu es venu. Le miel, puis le puzzle. Le tapis garde une pièce oubliée. Celle-là, je la mets. Tu as demandé, puis tu as continué.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1664,7 +1746,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Damien est allé vers eux. Il a dit le besoin. Papa et maman ont écouté.</t>
+          <t>narrateur|Raphaël est allé vers eux.
+narrateur|Il a dit le besoin.
+papa|Tu es venu nous voir.
+maman|Tu as dit : j'ai besoin d'aide.
+narrateur|Papa a tenu le bocal.
+narrateur|Maman a tendu la pièce.
+enfant-m|Aller vers eux.
+enfant-m|Dire le besoin.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+maman|Deux fois, tu es venu.
+maman|Le miel, puis le puzzle.
+narrateur|Le tapis garde une pièce oubliée.
+enfant-m|Celle-là, je la mets.
+maman|Tu as demandé, puis tu as continué.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1692,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le bocal est ouvert. Damien pose une pièce du puzzle.</t>
+          <t>Le bocal est ouvert, près du pain. Le puzzle a son ciel bleu. Raphaël range une pièce. Le chat est encore sur le muret. Tu as demandé deux fois. Le miel, puis le puzzle. J'ai dit le besoin. Oui. Et nous t'avons écouté. Le thé est tiède, maintenant. Encore une goutte de miel ? Une toute petite. Le miel brille encore. L'horloge fait encore tic-tac. La vitre est un peu froide sous le doigt. Le chat est parti. Il reviendra. Toi, tu es venu vers nous. C'est ça, le plus important.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1828,7 +1924,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le bocal est ouvert. Damien pose une pièce du puzzle.</t>
+          <t>narrateur|Le bocal est ouvert, près du pain.
+narrateur|Le puzzle a son ciel bleu.
+narrateur|Raphaël range une pièce.
+narrateur|Le chat est encore sur le muret.
+maman|Tu as demandé deux fois.
+papa|Le miel, puis le puzzle.
+enfant-m|J'ai dit le besoin.
+maman|Oui.
+maman|Et nous t'avons écouté.
+papa|Le thé est tiède, maintenant.
+enfant-m|Encore une goutte de miel ?
+papa|Une toute petite.
+narrateur|Le miel brille encore.
+narrateur|L'horloge fait encore tic-tac.
+narrateur|La vitre est un peu froide sous le doigt.
+enfant-m|Le chat est parti.
+maman|Il reviendra.
+papa|Toi, tu es venu vers nous.
+papa|C'est ça, le plus important.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1856,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai été vers vous. J'ai dit le besoin. Bravo, Raphaël. Le chat est parti. Les toits sont encore gris-bleu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1917,7 +2031,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -1996,7 +2110,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai été vers vous.
+enfant-m|J'ai dit le besoin.
+maman|Bravo, Raphaël.
+papa|Le chat est parti.
+narrateur|Les toits sont encore gris-bleu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2018,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2175,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-10.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Derrière la vitre, les toits du village sont gris-bleu. Le ciel est pâle, presque blanc. Une cheminée laisse un filet de fumée. Un chat marche sur le muret. Ses pattes ne font aucun bruit. Dans la cuisine, l'horloge fait tic-tac. Le bois de la table est lisse, un peu chaud. Papa et maman sont à table. Deux tasses fument tout doux. Ça sent le thé, Raphaël. Le pain est encore un peu chaud. La croûte craque sous le couteau. J'entends le chat ? Il est sur le muret. Il se promène, tout calme. Un bocal de miel brille près de l'assiette. Le miel est doré et épais. Je voudrais du miel. Il est dans le bocal, tout près. En ce moment, Raphaël prend le bocal. Le verre est lisse et froid. Il tourne le couvercle. Le couvercle reste collé. Ses mains sont un peu fatiguées. C'est trop difficile. Tu peux venir vers nous. Tu peux dire le besoin. Raphaël va vers eux. Il pose le bocal sur la table. J'ai besoin d'aide. Le couvercle est trop dur. Merci d'être venu le dire. On tient le bocal ensemble. Papa tient le bocal. Raphaël tourne un peu. Le couvercle fait clic. Bravo, Raphaël. Tu es allé vers nous. Tu as dit le besoin. Le miel sent bon. Une petite cuillère, tout doux. Le miel coule, lent et doré. Raphaël goûte une goutte. C'est sucré. Tu as demandé, et on a entendu. Plus tard, au salon, un puzzle attend. Les pièces sont sur le tapis. Le tapis est beige et doux. Une pièce bleue manque au ciel. Cette pièce ne rentre pas. Raphaël cherche, puis s'arrête. Il se souvient du bocal. Il va vers maman. Maman, j'ai besoin d'aide. Le puzzle est trop dur. Tu es venu vers nous. Tu as dit le besoin. C'est du bon travail. Demander, ce n'est pas être petit. C'est parler, tout simplement. Maman tend une pièce bleue. Raphaël la pose. Le ciel du puzzle devient entier. Elle rentre. Bravo. Aller vers eux, puis dire le besoin.</t>
+          <t>Derrière la vitre, les toits du village sont gris-bleu. Le ciel est pâle, presque blanc. Une cheminée laisse un filet de fumée. Un chat marche sur le muret. Ses pattes ne font aucun bruit. Dans la cuisine, l'horloge fait tic-tac. Le bois de la table est lisse, un peu chaud. Papa et maman sont à table. Deux tasses fument tout doux. Ça sent le thé, Raphaël. Le pain est encore un peu chaud. La croûte craque sous le couteau. J'entends le chat ? Il est sur le muret. Il se promène, tout calme. Un bocal de miel brille près de l'assiette. Le miel est doré et épais. Je voudrais du miel. Il est dans le bocal, tout près. En ce moment, Raphaël prend le bocal. Le verre est lisse et froid. Il tourne le couvercle. Le couvercle reste collé. Ses mains sont un peu fatiguées. C'est trop difficile. Tu peux venir vers nous. Tu peux dire le besoin. Raphaël va vers eux. Il pose le bocal sur la table. J'ai besoin d'aide. Le couvercle est trop dur. Merci d'être venu le dire. On tient le bocal ensemble. Papa tient le bocal. Raphaël tourne un peu. Le couvercle fait clic. Bravo, Raphaël. Tu es allé vers nous. Tu as dit le besoin. Le miel sent bon. Une petite cuillère, tout doux. Le miel coule, lent et doré. Raphaël goûte une goutte. C'est sucré. Tu as demandé, et on a entendu. Plus tard, au salon, un puzzle attend. Les pièces sont sur le tapis. Le tapis est beige et doux. Une pièce bleue manque au ciel. Cette pièce ne rentre pas. Raphaël cherche, puis s'arrête. Il se souvient du bocal. Il va vers maman. Maman, j'ai besoin d'aide. Le puzzle est trop dur. Tu es venu vers nous. Tu as dit le besoin. Demander, ce n'est pas être petit. C'est parler, tout simplement. Maman tend une pièce bleue. Raphaël la pose. Le ciel du puzzle devient entier. Elle rentre. Bravo. Aller vers eux, puis dire le besoin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Damien veut ouvrir le bocal. Le couvercle est dur. Damien sent ses mains fatiguées. Il va vers eux. Papa et maman sont dans la cuisine. Damien dit le besoin : j'ai besoin d'aide. Papa tient le bocal. Plus tard, le puzzle est trop dur. Damien va vers eux. Il dit le besoin. Maman écoute. Même leçon, autre objet. &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. Dire le besoin. Papa sourit. Maman tend une pièce.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Derrière la vitre, les toits du village sont gris-bleu. Le ciel est pâle, presque blanc. Une cheminée laisse un filet de fumée. Un chat marche sur le muret. Ses pattes ne font aucun bruit. Dans la cuisine, l'horloge fait tic-tac. Le bois de la table est lisse, un peu chaud. Papa et maman sont à table. Deux tasses fument tout doux. Ça sent le thé, Raphaël. Le pain est encore un peu chaud. La croûte craque sous le couteau. J'entends le chat ? Il est sur le muret. Il se promène, tout calme. Un bocal de miel brille près de l'assiette. Le miel est doré et épais. Je voudrais du miel. Il est dans le bocal, tout près. En ce moment, Raphaël prend le bocal. Le verre est lisse et froid. Il tourne le couvercle. Le couvercle reste collé. Ses mains sont un peu fatiguées. C'est trop difficile. Tu peux venir vers nous. Tu peux dire le besoin. Raphaël va vers eux. Il pose le bocal sur la table. J'ai besoin d'aide. Le couvercle est trop dur. Merci d'être venu le dire. On tient le bocal ensemble. Papa tient le bocal. Raphaël tourne un peu. Le couvercle fait clic. Bravo, Raphaël. Tu es allé vers nous. Tu as dit le besoin. Le miel sent bon. Une petite cuillère, tout doux. Le miel coule, lent et doré. Raphaël goûte une goutte. C'est sucré. Tu as demandé, et on a entendu. Plus tard, au salon, un puzzle attend. Les pièces sont sur le tapis. Le tapis est beige et doux. Une pièce bleue manque au ciel. Cette pièce ne rentre pas. Raphaël cherche, puis s'arrête. Il se souvient du bocal. Il va vers maman. Maman, j'ai besoin d'aide. Le puzzle est trop dur. Tu es venu vers nous. Tu as dit le besoin. Demander, ce n'est pas être petit. C'est parler, tout simplement. Maman tend une pièce bleue. Raphaël la pose. Le ciel du puzzle devient entier. Elle rentre. Bravo. Aller vers eux, puis dire le besoin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1381,7 +1381,6 @@
 enfant-m|Le puzzle est trop dur.
 maman|Tu es venu vers nous.
 maman|Tu as dit le besoin.
-maman|C'est du bon travail.
 papa|Demander, ce n'est pas être petit.
 papa|C'est parler, tout simplement.
 narrateur|Maman tend une pièce bleue.
@@ -1426,7 +1425,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est trop difficile. Que fait Damien ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>C'est trop difficile. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1581,7 +1580,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est allé vers eux. Il a dit le besoin. Tu es venu nous voir. Tu as dit : j'ai besoin d'aide. Papa a tenu le bocal. Maman a tendu la pièce. Aller vers eux. Dire le besoin. Bravo, Raphaël. Tu as fait du bon travail. Deux fois, tu es venu. Le miel, puis le puzzle. Le tapis garde une pièce oubliée. Celle-là, je la mets. Tu as demandé, puis tu as continué.</t>
+          <t>Raphaël est allé vers eux. Il a dit le besoin. Tu es venu nous voir. Tu as dit : j'ai besoin d'aide. Papa a tenu le bocal. Maman a tendu la pièce. Aller vers eux. Dire le besoin. Bravo, Raphaël. Deux fois, tu es venu. Le miel, puis le puzzle. Le tapis garde une pièce oubliée. Celle-là, je la mets. Tu as demandé, puis tu as continué.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Damien est allé vers eux. Il a dit le besoin. Papa et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est allé vers eux. Il a dit le besoin. Tu es venu nous voir. Tu as dit : j'ai besoin d'aide. Papa a tenu le bocal. Maman a tendu la pièce. Aller vers eux. Dire le besoin. Bravo, Raphaël. Deux fois, tu es venu. Le miel, puis le puzzle. Le tapis garde une pièce oubliée. Celle-là, je la mets. Tu as demandé, puis tu as continué.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1753,6 @@
 enfant-m|Aller vers eux.
 enfant-m|Dire le besoin.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 maman|Deux fois, tu es venu.
 maman|Le miel, puis le puzzle.
 narrateur|Le tapis garde une pièce oubliée.
@@ -1763,7 +1760,6 @@
 maman|Tu as demandé, puis tu as continué.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le bocal est ouvert. Damien pose une pièce du puzzle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bocal est ouvert, près du pain. Le puzzle a son ciel bleu. Raphaël range une pièce. Le chat est encore sur le muret. Tu as demandé deux fois. Le miel, puis le puzzle. J'ai dit le besoin. Oui. Et nous t'avons écouté. Le thé est tiède, maintenant. Encore une goutte de miel ? Une toute petite. Le miel brille encore. L'horloge fait encore tic-tac. La vitre est un peu froide sous le doigt. Le chat est parti. Il reviendra. Toi, tu es venu vers nous. C'est ça, le plus important.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,7 +1941,6 @@
 papa|C'est ça, le plus important.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1970,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai été vers vous. J'ai dit le besoin. Bravo, Raphaël. Le chat est parti. Les toits sont encore gris-bleu. L'histoire est finie.</t>
+          <t>J'ai été vers vous. J'ai dit le besoin. Bravo, Raphaël. Le chat est parti. Les toits sont encore gris-bleu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai été vers vous. J'ai dit le besoin. Bravo, Raphaël. Le chat est parti. Les toits sont encore gris-bleu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,11 +2109,9 @@
 enfant-m|J'ai dit le besoin.
 maman|Bravo, Raphaël.
 papa|Le chat est parti.
-narrateur|Les toits sont encore gris-bleu.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les toits sont encore gris-bleu.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2137,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-10.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine et salon</t>
+          <t>cuisine puis salon</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Damien, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
